--- a/05_finance_payments.xlsx
+++ b/05_finance_payments.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="99">
   <si>
     <t>payment_id</t>
   </si>
@@ -149,6 +149,165 @@
   </si>
   <si>
     <t>P017</t>
+  </si>
+  <si>
+    <t>P018</t>
+  </si>
+  <si>
+    <t>P019</t>
+  </si>
+  <si>
+    <t>CTR014</t>
+  </si>
+  <si>
+    <t>P020</t>
+  </si>
+  <si>
+    <t>CTR015</t>
+  </si>
+  <si>
+    <t>P021</t>
+  </si>
+  <si>
+    <t>CTR016</t>
+  </si>
+  <si>
+    <t>P022</t>
+  </si>
+  <si>
+    <t>CTR017</t>
+  </si>
+  <si>
+    <t>P023</t>
+  </si>
+  <si>
+    <t>CTR018</t>
+  </si>
+  <si>
+    <t>P024</t>
+  </si>
+  <si>
+    <t>CTR019</t>
+  </si>
+  <si>
+    <t>P025</t>
+  </si>
+  <si>
+    <t>CTR020</t>
+  </si>
+  <si>
+    <t>P026</t>
+  </si>
+  <si>
+    <t>CTR021</t>
+  </si>
+  <si>
+    <t>P027</t>
+  </si>
+  <si>
+    <t>CTR022</t>
+  </si>
+  <si>
+    <t>P028</t>
+  </si>
+  <si>
+    <t>CTR023</t>
+  </si>
+  <si>
+    <t>P029</t>
+  </si>
+  <si>
+    <t>CTR024</t>
+  </si>
+  <si>
+    <t>P030</t>
+  </si>
+  <si>
+    <t>CTR025</t>
+  </si>
+  <si>
+    <t>P031</t>
+  </si>
+  <si>
+    <t>CTR026</t>
+  </si>
+  <si>
+    <t>P032</t>
+  </si>
+  <si>
+    <t>CTR027</t>
+  </si>
+  <si>
+    <t>P033</t>
+  </si>
+  <si>
+    <t>CTR028</t>
+  </si>
+  <si>
+    <t>P034</t>
+  </si>
+  <si>
+    <t>lead</t>
+  </si>
+  <si>
+    <t>CTR029</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>P035</t>
+  </si>
+  <si>
+    <t>CTR030</t>
+  </si>
+  <si>
+    <t>P036</t>
+  </si>
+  <si>
+    <t>CTR031</t>
+  </si>
+  <si>
+    <t>P037</t>
+  </si>
+  <si>
+    <t>CTR032</t>
+  </si>
+  <si>
+    <t>P038</t>
+  </si>
+  <si>
+    <t>CTR033</t>
+  </si>
+  <si>
+    <t>P039</t>
+  </si>
+  <si>
+    <t>CTR034</t>
+  </si>
+  <si>
+    <t>P040</t>
+  </si>
+  <si>
+    <t>CTR035</t>
+  </si>
+  <si>
+    <t>P041</t>
+  </si>
+  <si>
+    <t>CTR036</t>
+  </si>
+  <si>
+    <t>P042</t>
+  </si>
+  <si>
+    <t>CTR037</t>
+  </si>
+  <si>
+    <t>P043</t>
+  </si>
+  <si>
+    <t>CTR038</t>
   </si>
 </sst>
 </file>
@@ -159,7 +318,7 @@
     <numFmt numFmtId="164" formatCode="dd.mm.yyyy"/>
     <numFmt numFmtId="165" formatCode="d.m.yyyy"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -170,6 +329,11 @@
       <sz val="12.0"/>
       <color theme="1"/>
       <name val="&quot;Segoe UI&quot;"/>
+    </font>
+    <font>
+      <sz val="12.0"/>
+      <color theme="1"/>
+      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="2">
@@ -186,7 +350,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -197,6 +361,9 @@
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
   </cellXfs>
@@ -415,6 +582,14 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="2" max="2" width="11.75"/>
+    <col customWidth="1" min="3" max="3" width="11.0"/>
+    <col customWidth="1" min="4" max="4" width="7.63"/>
+    <col customWidth="1" min="5" max="5" width="8.63"/>
+    <col customWidth="1" min="6" max="6" width="13.63"/>
+    <col customWidth="1" min="8" max="8" width="16.5"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
@@ -884,6 +1059,682 @@
         <v>12</v>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B19" s="1">
+        <v>1009.0</v>
+      </c>
+      <c r="C19" s="2">
+        <v>45727.0</v>
+      </c>
+      <c r="D19" s="4">
+        <v>50000.0</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B20" s="1">
+        <v>1016.0</v>
+      </c>
+      <c r="C20" s="2">
+        <v>45721.0</v>
+      </c>
+      <c r="D20" s="1">
+        <v>50000.0</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B21" s="1">
+        <v>1017.0</v>
+      </c>
+      <c r="C21" s="2">
+        <v>45679.0</v>
+      </c>
+      <c r="D21" s="1">
+        <v>200000.0</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B22" s="1">
+        <v>1018.0</v>
+      </c>
+      <c r="C22" s="2">
+        <v>45693.0</v>
+      </c>
+      <c r="D22" s="1">
+        <v>75000.0</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B23" s="1">
+        <v>1019.0</v>
+      </c>
+      <c r="C23" s="2">
+        <v>45706.0</v>
+      </c>
+      <c r="D23" s="1">
+        <v>60000.0</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B24" s="1">
+        <v>1020.0</v>
+      </c>
+      <c r="C24" s="2">
+        <v>45710.0</v>
+      </c>
+      <c r="D24" s="1">
+        <v>240000.0</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B25" s="1">
+        <v>1021.0</v>
+      </c>
+      <c r="C25" s="2">
+        <v>45713.0</v>
+      </c>
+      <c r="D25" s="1">
+        <v>125000.0</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B26" s="1">
+        <v>1022.0</v>
+      </c>
+      <c r="C26" s="2">
+        <v>45717.0</v>
+      </c>
+      <c r="D26" s="1">
+        <v>66000.0</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B27" s="1">
+        <v>1023.0</v>
+      </c>
+      <c r="C27" s="2">
+        <v>45721.0</v>
+      </c>
+      <c r="D27" s="1">
+        <v>120000.0</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B28" s="1">
+        <v>1024.0</v>
+      </c>
+      <c r="C28" s="2">
+        <v>45724.0</v>
+      </c>
+      <c r="D28" s="1">
+        <v>160000.0</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B29" s="1">
+        <v>1025.0</v>
+      </c>
+      <c r="C29" s="2">
+        <v>45726.0</v>
+      </c>
+      <c r="D29" s="1">
+        <v>150000.0</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B30" s="1">
+        <v>1026.0</v>
+      </c>
+      <c r="C30" s="2">
+        <v>45728.0</v>
+      </c>
+      <c r="D30" s="1">
+        <v>44000.0</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B31" s="1">
+        <v>1027.0</v>
+      </c>
+      <c r="C31" s="2">
+        <v>45731.0</v>
+      </c>
+      <c r="D31" s="1">
+        <v>75000.0</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B32" s="1">
+        <v>1028.0</v>
+      </c>
+      <c r="C32" s="2">
+        <v>45734.0</v>
+      </c>
+      <c r="D32" s="1">
+        <v>280000.0</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B33" s="1">
+        <v>1029.0</v>
+      </c>
+      <c r="C33" s="2">
+        <v>45736.0</v>
+      </c>
+      <c r="D33" s="1">
+        <v>100000.0</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B34" s="1">
+        <v>1030.0</v>
+      </c>
+      <c r="C34" s="2">
+        <v>45738.0</v>
+      </c>
+      <c r="D34" s="1">
+        <v>45000.0</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B35" s="1">
+        <v>1031.0</v>
+      </c>
+      <c r="C35" s="2">
+        <v>45739.0</v>
+      </c>
+      <c r="D35" s="1">
+        <v>200000.0</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B36" s="1">
+        <v>1032.0</v>
+      </c>
+      <c r="C36" s="2">
+        <v>45740.0</v>
+      </c>
+      <c r="D36" s="1">
+        <v>50000.0</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B37" s="1">
+        <v>1033.0</v>
+      </c>
+      <c r="C37" s="2">
+        <v>45741.0</v>
+      </c>
+      <c r="D37" s="1">
+        <v>88000.0</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B38" s="1">
+        <v>1034.0</v>
+      </c>
+      <c r="C38" s="2">
+        <v>45742.0</v>
+      </c>
+      <c r="D38" s="1">
+        <v>90000.0</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B39" s="1">
+        <v>1035.0</v>
+      </c>
+      <c r="C39" s="2">
+        <v>45743.0</v>
+      </c>
+      <c r="D39" s="1">
+        <v>320000.0</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="H39" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B40" s="1">
+        <v>1036.0</v>
+      </c>
+      <c r="C40" s="2">
+        <v>45744.0</v>
+      </c>
+      <c r="D40" s="1">
+        <v>125000.0</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="H40" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B41" s="1">
+        <v>1037.0</v>
+      </c>
+      <c r="C41" s="2">
+        <v>45745.0</v>
+      </c>
+      <c r="D41" s="1">
+        <v>66000.0</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="H41" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B42" s="1">
+        <v>1038.0</v>
+      </c>
+      <c r="C42" s="2">
+        <v>45746.0</v>
+      </c>
+      <c r="D42" s="1">
+        <v>60000.0</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="H42" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B43" s="1">
+        <v>1039.0</v>
+      </c>
+      <c r="C43" s="2">
+        <v>45747.0</v>
+      </c>
+      <c r="D43" s="1">
+        <v>240000.0</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B44" s="1">
+        <v>1040.0</v>
+      </c>
+      <c r="C44" s="2">
+        <v>45747.0</v>
+      </c>
+      <c r="D44" s="1">
+        <v>75000.0</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="H44" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
